--- a/Data/Perth_Rainfall-2024.xlsx
+++ b/Data/Perth_Rainfall-2024.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\61488\Documents\CITS1501\CITS1501\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\61488\Documents\GitHub\CITS1501-project-1\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A9FB29-8C74-49F2-B56E-37E06BF9C25B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8064" yWindow="3636" windowWidth="11712" windowHeight="5640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rainfall" sheetId="1" r:id="rId1"/>
